--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,670 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9925,0.0005,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0051,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0235,0.0003,0.0000,0.9928</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9880,0.0010,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0090,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0154,0.0004,0.0000,0.9959</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.9994,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9889,0.0003,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.0012,0.9906,0.0011</t>
+  </si>
+  <si>
+    <t>0.5432,0.0010,0.5237,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1361,0.8168,0.0002,0.0042</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9856,0.0003,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.0995,0.0015,0.9076,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0127,0.0002,0.9842,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.6474,0.3004,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.4989,0.0256,0.2735,0.0024</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9994,0.0019</t>
+  </si>
+  <si>
+    <t>0.0040,0.9589,0.1420,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9164,0.0044,0.0505,0.0008</t>
+  </si>
+  <si>
+    <t>0.9823,0.0122,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9952,0.1566,0.0000</t>
+  </si>
+  <si>
+    <t>0.0275,0.4648,0.0363,0.0144</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0182,0.9821,0.0006</t>
+  </si>
+  <si>
+    <t>0.7420,0.0000,0.1115,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0428,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9972,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.5362,0.0156,0.8839</t>
+  </si>
+  <si>
+    <t>0.0001,0.9947,0.0001,0.0066</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.2757,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0026,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0116,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0074,0.0047,0.9851,0.0035</t>
+  </si>
+  <si>
+    <t>0.0068,0.0003,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.5886,0.0014,0.3295,0.0047</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.0004,0.9866,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.9964,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9913,0.0003,0.0066,0.0001</t>
+  </si>
+  <si>
+    <t>0.6974,0.0054,0.1660,0.0027</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9805,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9778,0.8906,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.1308,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9364,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0009,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0005,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9955,0.7994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8154,0.9745,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9841,0.6905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.4949,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9949,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9784,0.9460,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0003</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9850,0.0002,0.0143,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0021,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.9559,0.0003,0.0430,0.0002</t>
-  </si>
-  <si>
-    <t>0.0071,0.0002,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
+    <t>0.9969,0.0033,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0063,0.0057,0.9903,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9967,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.3585,0.6573,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.2565,0.0021,0.6304,0.0029</t>
+  </si>
+  <si>
+    <t>0.8144,0.0007,0.1916,0.0004</t>
+  </si>
+  <si>
+    <t>0.7336,0.0126,0.0694,0.0056</t>
+  </si>
+  <si>
+    <t>0.8608,0.0145,0.0470,0.0078</t>
+  </si>
+  <si>
+    <t>0.0001,0.4516,0.0003,0.9770</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0006,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0035,0.9919,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.7753,0.0051,0.1770,0.0026</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0058,0.0006,0.9920,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.1965,0.8001,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9308,0.0522,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0036</t>
-  </si>
-  <si>
-    <t>0.0039,0.9506,0.1587,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9859,0.0025,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.4088,0.6304,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.0007,0.9894,0.1220,0.0000</t>
-  </si>
-  <si>
-    <t>0.0237,0.2782,0.1891,0.0106</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0038,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.4370,0.0000,0.2401,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.0204,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9845,0.0014,0.8991</t>
-  </si>
-  <si>
-    <t>0.0002,0.9981,0.0003,0.0032</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0144,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0029,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0029,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.1275,0.0027,0.8772,0.0030</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0008,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.0068,0.9869,0.0025</t>
-  </si>
-  <si>
-    <t>0.9957,0.0040,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0013,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9767,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0615,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0031,0.9881,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9935,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0167,0.9822,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0002,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.8931,0.0004,0.0728,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9734,0.8955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.6879,0.8789,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.5749,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9957,0.8456,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0005,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0014,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.7071,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9148,0.9461,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9664,0.1167,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.9703,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9867,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9896,0.3798,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0009,0.0000,0.0000</t>
+    <t>0.0000,0.9999,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9822,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9991,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6665,0.3662,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9601,0.0323,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0010,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0008,0.0046,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.0000,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9971,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9975,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0286,0.9592,0.0053,0.0008</t>
-  </si>
-  <si>
-    <t>0.4337,0.0012,0.5265,0.0016</t>
-  </si>
-  <si>
-    <t>0.7822,0.0069,0.1186,0.0023</t>
-  </si>
-  <si>
-    <t>0.8272,0.0133,0.0551,0.0051</t>
-  </si>
-  <si>
-    <t>0.1120,0.0029,0.8542,0.0043</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9896,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4149,0.6354,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.9706,0.0193,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9967,0.0005,0.0012,0.0001</t>
-  </si>
-  <si>
     <t>0.9996,0.0000,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.4388,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0859,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.1875,0.0057,0.8335,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5428,0.0008,0.3682,0.0039</t>
-  </si>
-  <si>
-    <t>0.0877,0.0001,0.9578,0.0001</t>
-  </si>
-  <si>
-    <t>0.0643,0.0006,0.9573,0.0002</t>
-  </si>
-  <si>
-    <t>0.0178,0.0009,0.0003,0.9955</t>
-  </si>
-  <si>
-    <t>0.0037,0.0002,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.0001,0.9986,0.0529,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.1335,0.8882,0.0019,0.0070</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.3123,0.7097,0.0022,0.0044</t>
-  </si>
-  <si>
-    <t>0.0878,0.0001,0.0005,0.9484</t>
-  </si>
-  <si>
-    <t>0.0007,0.0058,0.9976,0.0046</t>
-  </si>
-  <si>
-    <t>0.6442,0.0002,0.0582,0.0774</t>
-  </si>
-  <si>
-    <t>0.9974,0.0007,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.5765,0.4867,0.0017,0.0004</t>
+    <t>0.0000,0.1034,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8339,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0043,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7454,0.0010,0.2281,0.0005</t>
+  </si>
+  <si>
+    <t>0.1866,0.0001,0.8946,0.0001</t>
+  </si>
+  <si>
+    <t>0.2746,0.0013,0.8031,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.0006,0.0034,0.9968</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.9907,0.7954,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0015,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0869,0.9215,0.0006,0.0120</t>
+  </si>
+  <si>
+    <t>0.0430,0.9469,0.0053,0.0044</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0295,0.0001,0.0001,0.9894</t>
+  </si>
+  <si>
+    <t>0.0006,0.0039,0.9976,0.0065</t>
+  </si>
+  <si>
+    <t>0.9049,0.0001,0.0076,0.0252</t>
+  </si>
+  <si>
+    <t>0.0199,0.9778,0.0015,0.0002</t>
   </si>
   <si>
     <t>0.9996,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9980,0.0001,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.2531,0.6929,0.0123,0.0025</t>
-  </si>
-  <si>
-    <t>0.9835,0.0017,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9925,0.0031,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9738,0.0260,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9155,0.0972,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9570,0.0463,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0064,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0015,0.0069,0.0003</t>
+    <t>0.9985,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.1943,0.8273,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9928,0.0022,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9194,0.0340,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.9058,0.1155,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.8136,0.2765,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.8687,0.0168,0.0766,0.0008</t>
+  </si>
+  <si>
+    <t>0.9956,0.0037,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0043,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0098,0.9905,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0661,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0078,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0356,0.0013,0.9661,0.0014</t>
+  </si>
+  <si>
+    <t>0.0009,0.0020,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0515,0.0054,0.9254,0.0013</t>
+  </si>
+  <si>
+    <t>0.0459,0.0023,0.9514,0.0002</t>
+  </si>
+  <si>
+    <t>0.0099,0.0404,0.9586,0.0003</t>
+  </si>
+  <si>
+    <t>0.9859,0.0009,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.9477,0.0002,0.0329,0.0016</t>
+  </si>
+  <si>
+    <t>0.5842,0.0005,0.5222,0.0001</t>
+  </si>
+  <si>
+    <t>0.0408,0.9671,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9986,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5576,0.5795,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9643,0.0278,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.5115,0.5341,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9842,0.0018,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9863,0.0021,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8988,0.0069,0.0604,0.0007</t>
+  </si>
+  <si>
+    <t>0.5370,0.0181,0.3490,0.0034</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.2109,0.0022,0.6769,0.0029</t>
+  </si>
+  <si>
+    <t>0.0019,0.0014,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0314,0.9919,0.0015</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9922,0.0052,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0099,0.0427,0.9674,0.0013</t>
+  </si>
+  <si>
+    <t>0.9692,0.0002,0.0114,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0045,0.0054,0.9898,0.0020</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0034,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0390,0.0023,0.9593,0.0019</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.6797,0.0024,0.2829,0.0015</t>
-  </si>
-  <si>
-    <t>0.0192,0.0141,0.9569,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.0129,0.9788,0.0010</t>
-  </si>
-  <si>
-    <t>0.7574,0.0209,0.1638,0.0008</t>
-  </si>
-  <si>
-    <t>0.7408,0.0016,0.2576,0.0012</t>
-  </si>
-  <si>
-    <t>0.0847,0.0015,0.9296,0.0005</t>
-  </si>
-  <si>
-    <t>0.0357,0.9741,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0182,0.9829,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.3792,0.7124,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9338,0.0644,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0304,0.9712,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9773,0.0043,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9220,0.0057,0.0271,0.0024</t>
-  </si>
-  <si>
-    <t>0.9855,0.0010,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9072,0.0011,0.0654,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0342,0.0019,0.9455,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0020,0.9913,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.0060,0.9894,0.0038</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0016,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.3858,0.0206,0.4434,0.0013</t>
-  </si>
-  <si>
-    <t>0.9490,0.0001,0.0255,0.0021</t>
-  </si>
-  <si>
-    <t>0.0007,0.0037,0.9979,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.8189,0.4509,0.0022</t>
-  </si>
-  <si>
-    <t>0.1164,0.0002,0.8998,0.0004</t>
+    <t>0.0006,0.0186,0.9946,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0026,0.0020,0.9949,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0041,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.9920,0.0002,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9934,0.0000,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0023,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0623,0.0041,0.9263,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.0083,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0029,0.0057,0.9879,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.0010,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.3138,0.0030,0.5691,0.0129</t>
-  </si>
-  <si>
-    <t>0.0027,0.0006,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.0000,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.9876,0.0004,0.0001,0.0121</t>
-  </si>
-  <si>
-    <t>0.0001,0.0427,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0082,0.0000,0.0001,0.9975</t>
+    <t>0.0091,0.0006,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.0132,0.0024,0.9833,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.9802,0.0003,0.0097,0.0005</t>
+  </si>
+  <si>
+    <t>0.8711,0.0000,0.1471,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0026,0.9950,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0075,0.9945,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.0016,0.9955,0.0012</t>
+  </si>
+  <si>
+    <t>0.0424,0.0005,0.9488,0.0030</t>
+  </si>
+  <si>
+    <t>0.0065,0.0051,0.9863,0.0030</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9982,0.0005</t>
+  </si>
+  <si>
+    <t>0.9796,0.0006,0.0003,0.0171</t>
+  </si>
+  <si>
+    <t>0.0000,0.0062,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0058,0.0001,0.0004,0.9977</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.8467,0.0028,0.0747,0.0199</t>
+    <t>0.9841,0.0009,0.0016,0.0033</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1885,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1913,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1927,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1941,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1955,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1969,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1983,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1997,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2011,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2039,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,10 +2068,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2067,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2081,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2095,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2109,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2137,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2151,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2165,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,10 +2194,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2193,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2207,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2221,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2235,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2249,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,10 +2292,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2291,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2305,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2319,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2333,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2361,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,10 +2390,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2389,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2403,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2431,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2445,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2459,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,10 +2488,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2487,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2515,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2529,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2543,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2557,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2571,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2585,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,10 +2614,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2613,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2627,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2641,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2655,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2669,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2683,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2697,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2711,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2725,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2739,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2753,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2767,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2781,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2795,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2823,7 +2841,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2837,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2851,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,10 +2894,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2893,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2907,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2921,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2935,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2949,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2963,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2977,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,7 +3009,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3005,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,10 +3034,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3030,10 +3048,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3047,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3075,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3089,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3103,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3117,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3131,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3145,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3159,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3173,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3187,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3201,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3215,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3229,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3243,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3271,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3285,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3299,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3313,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3327,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3341,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3355,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3369,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3383,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3397,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3411,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3425,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3439,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3453,7 +3471,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3467,7 +3485,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3481,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,10 +3510,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3509,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3523,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3537,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3551,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3579,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,10 +3608,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3607,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3621,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3635,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3649,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3663,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3677,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3691,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3705,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3719,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3733,7 +3751,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3744,10 +3762,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3761,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3775,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3789,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3817,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,7 +3849,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3845,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3859,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3873,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3887,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,10 +3916,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3915,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3929,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3943,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>393</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3957,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3971,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3985,7 +4003,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3999,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4013,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4027,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4041,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4069,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4083,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4097,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4139,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4153,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4167,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4181,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4195,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>407</v>
+        <v>358</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4209,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4223,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4237,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4251,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4265,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4279,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4293,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4321,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4335,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4349,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4363,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4377,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4391,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4405,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4419,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4433,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4447,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4461,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4475,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4489,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4503,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,10 +4532,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4531,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4545,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4573,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4615,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,10 +4644,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4643,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4699,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4713,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4741,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4755,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4769,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4783,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4797,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4811,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4825,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4839,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4853,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4867,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4881,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4895,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4909,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4923,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4934,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4951,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4965,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>288</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4979,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,10 +5008,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5007,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5021,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5035,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5049,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5063,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5105,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5119,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5133,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5147,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5161,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5175,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>471</v>
+        <v>358</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5189,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>322</v>
+        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5203,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>275</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5217,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5231,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5245,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5259,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5273,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5287,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5301,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5315,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5329,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5343,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5357,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5371,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5385,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>484</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5399,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>490</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5413,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
